--- a/output/yearly_total_coral_cover_iteration_51_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_51_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.273431264936661</v>
+        <v>1.253334889430729</v>
       </c>
       <c r="C3" t="n">
-        <v>4.670131505010956</v>
+        <v>4.663416350713907</v>
       </c>
       <c r="D3" t="n">
-        <v>6.141200139387531</v>
+        <v>6.073302468161822</v>
       </c>
       <c r="E3" t="n">
-        <v>12.08476290933515</v>
+        <v>11.99005370830646</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.430252127326744</v>
+        <v>1.375329744372835</v>
       </c>
       <c r="C4" t="n">
-        <v>5.250318808628117</v>
+        <v>5.209189949018015</v>
       </c>
       <c r="D4" t="n">
-        <v>6.369729584434169</v>
+        <v>6.313290816984754</v>
       </c>
       <c r="E4" t="n">
-        <v>13.05030052038903</v>
+        <v>12.8978105103756</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.633445237084567</v>
+        <v>1.537831219021388</v>
       </c>
       <c r="C5" t="n">
-        <v>6.049924508947325</v>
+        <v>5.948460690427732</v>
       </c>
       <c r="D5" t="n">
-        <v>6.636280408708608</v>
+        <v>6.618294968708422</v>
       </c>
       <c r="E5" t="n">
-        <v>14.3196501547405</v>
+        <v>14.10458687815754</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.867637142177332</v>
+        <v>1.725357258795342</v>
       </c>
       <c r="C6" t="n">
-        <v>7.10381877603642</v>
+        <v>6.87991049245647</v>
       </c>
       <c r="D6" t="n">
-        <v>6.981494980984152</v>
+        <v>6.963768274663341</v>
       </c>
       <c r="E6" t="n">
-        <v>15.9529508991979</v>
+        <v>15.56903602591515</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.139802202171981</v>
+        <v>1.938828360324086</v>
       </c>
       <c r="C7" t="n">
-        <v>8.387000684404372</v>
+        <v>8.046984635068569</v>
       </c>
       <c r="D7" t="n">
-        <v>7.337240243494081</v>
+        <v>7.330250110069332</v>
       </c>
       <c r="E7" t="n">
-        <v>17.86404313007043</v>
+        <v>17.31606310546199</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.35632152707343</v>
+        <v>1.169102965085156</v>
       </c>
       <c r="C8" t="n">
-        <v>6.177140873999686</v>
+        <v>5.815944284696511</v>
       </c>
       <c r="D8" t="n">
-        <v>5.499076769355905</v>
+        <v>5.50428907573807</v>
       </c>
       <c r="E8" t="n">
-        <v>13.03253917042902</v>
+        <v>12.48933632551974</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.708499788631744</v>
+        <v>1.461307662048091</v>
       </c>
       <c r="C9" t="n">
-        <v>7.815175397762556</v>
+        <v>7.372448894738579</v>
       </c>
       <c r="D9" t="n">
-        <v>5.88951694188305</v>
+        <v>6.014789544846431</v>
       </c>
       <c r="E9" t="n">
-        <v>15.41319212827735</v>
+        <v>14.8485461016331</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.063053919163208</v>
+        <v>1.748033763327794</v>
       </c>
       <c r="C10" t="n">
-        <v>9.612985372316368</v>
+        <v>9.182633735033027</v>
       </c>
       <c r="D10" t="n">
-        <v>6.258585932749231</v>
+        <v>6.560214628044259</v>
       </c>
       <c r="E10" t="n">
-        <v>17.93462522422881</v>
+        <v>17.49088212640508</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.404454042799076</v>
+        <v>2.035937439392223</v>
       </c>
       <c r="C11" t="n">
-        <v>11.50603530188707</v>
+        <v>11.15343295361698</v>
       </c>
       <c r="D11" t="n">
-        <v>6.688879563948496</v>
+        <v>7.177566151027703</v>
       </c>
       <c r="E11" t="n">
-        <v>20.59936890863464</v>
+        <v>20.3669365440369</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.742647254903956</v>
+        <v>2.31310632847629</v>
       </c>
       <c r="C12" t="n">
-        <v>13.46825442941757</v>
+        <v>13.13529563803789</v>
       </c>
       <c r="D12" t="n">
-        <v>7.072815782949612</v>
+        <v>7.731084840138862</v>
       </c>
       <c r="E12" t="n">
-        <v>23.28371746727114</v>
+        <v>23.17948680665304</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.035056923195927</v>
+        <v>2.553405596654724</v>
       </c>
       <c r="C13" t="n">
-        <v>15.41535763328574</v>
+        <v>15.0776492148718</v>
       </c>
       <c r="D13" t="n">
-        <v>7.440903428655082</v>
+        <v>8.13463088472912</v>
       </c>
       <c r="E13" t="n">
-        <v>25.89131798513675</v>
+        <v>25.76568569625564</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.73302031744464</v>
+        <v>1.465376258312874</v>
       </c>
       <c r="C14" t="n">
-        <v>10.63583247629712</v>
+        <v>10.3565252544389</v>
       </c>
       <c r="D14" t="n">
-        <v>5.640052203604544</v>
+        <v>6.217800910076749</v>
       </c>
       <c r="E14" t="n">
-        <v>18.0089049973463</v>
+        <v>18.03970242282852</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.75450095721356</v>
+        <v>1.474928663475195</v>
       </c>
       <c r="C15" t="n">
-        <v>11.58418112364545</v>
+        <v>11.29438883630588</v>
       </c>
       <c r="D15" t="n">
-        <v>5.572625771276873</v>
+        <v>6.239831328560047</v>
       </c>
       <c r="E15" t="n">
-        <v>18.91130785213588</v>
+        <v>19.00914882834112</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.004404835329586</v>
+        <v>1.684031107002724</v>
       </c>
       <c r="C16" t="n">
-        <v>13.77846578245341</v>
+        <v>13.3073545116165</v>
       </c>
       <c r="D16" t="n">
-        <v>5.939141641703334</v>
+        <v>6.6905615170568</v>
       </c>
       <c r="E16" t="n">
-        <v>21.72201225948633</v>
+        <v>21.68194713567602</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.586474837631718</v>
+        <v>1.334813631125091</v>
       </c>
       <c r="C17" t="n">
-        <v>12.6961576608606</v>
+        <v>12.18131934727653</v>
       </c>
       <c r="D17" t="n">
-        <v>5.437723819236319</v>
+        <v>6.194130972927359</v>
       </c>
       <c r="E17" t="n">
-        <v>19.72035631772864</v>
+        <v>19.71026395132898</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.77446970551794</v>
+        <v>1.492609939628681</v>
       </c>
       <c r="C18" t="n">
-        <v>14.9079959686205</v>
+        <v>14.11818975803098</v>
       </c>
       <c r="D18" t="n">
-        <v>5.762211070443974</v>
+        <v>6.574597478231167</v>
       </c>
       <c r="E18" t="n">
-        <v>22.44467674458241</v>
+        <v>22.18539717589083</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.746548800809161</v>
+        <v>1.472621556370216</v>
       </c>
       <c r="C19" t="n">
-        <v>15.99424089850734</v>
+        <v>14.99974029158236</v>
       </c>
       <c r="D19" t="n">
-        <v>5.78371134516698</v>
+        <v>6.645420757615532</v>
       </c>
       <c r="E19" t="n">
-        <v>23.52450104448348</v>
+        <v>23.11778260556811</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.90836045742312</v>
+        <v>1.612874033398915</v>
       </c>
       <c r="C20" t="n">
-        <v>18.33751558891179</v>
+        <v>17.0161322663808</v>
       </c>
       <c r="D20" t="n">
-        <v>6.094807557688708</v>
+        <v>7.015146943034881</v>
       </c>
       <c r="E20" t="n">
-        <v>26.34068360402362</v>
+        <v>25.64415324281459</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.115265392024377</v>
+        <v>0.9446278235492386</v>
       </c>
       <c r="C21" t="n">
-        <v>13.44557477089741</v>
+        <v>12.26800766956153</v>
       </c>
       <c r="D21" t="n">
-        <v>5.051995146237747</v>
+        <v>5.859296100916941</v>
       </c>
       <c r="E21" t="n">
-        <v>19.61283530915953</v>
+        <v>19.07193159402771</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_51_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_51_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.253334889430729</v>
+        <v>1.296983392361542</v>
       </c>
       <c r="C3" t="n">
-        <v>4.663416350713907</v>
+        <v>4.588587540696215</v>
       </c>
       <c r="D3" t="n">
-        <v>6.073302468161822</v>
+        <v>6.070278685232742</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99005370830646</v>
+        <v>11.9558496182905</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.375329744372835</v>
+        <v>1.486449823029952</v>
       </c>
       <c r="C4" t="n">
-        <v>5.209189949018015</v>
+        <v>5.02549643309534</v>
       </c>
       <c r="D4" t="n">
-        <v>6.313290816984754</v>
+        <v>6.305201906900639</v>
       </c>
       <c r="E4" t="n">
-        <v>12.8978105103756</v>
+        <v>12.81714816302593</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.537831219021388</v>
+        <v>1.740957271283943</v>
       </c>
       <c r="C5" t="n">
-        <v>5.948460690427732</v>
+        <v>5.589195531704904</v>
       </c>
       <c r="D5" t="n">
-        <v>6.618294968708422</v>
+        <v>6.705478814784059</v>
       </c>
       <c r="E5" t="n">
-        <v>14.10458687815754</v>
+        <v>14.03563161777291</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.725357258795342</v>
+        <v>2.015756300555287</v>
       </c>
       <c r="C6" t="n">
-        <v>6.87991049245647</v>
+        <v>6.258652704346712</v>
       </c>
       <c r="D6" t="n">
-        <v>6.963768274663341</v>
+        <v>7.088295739512284</v>
       </c>
       <c r="E6" t="n">
-        <v>15.56903602591515</v>
+        <v>15.36270474441428</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.938828360324086</v>
+        <v>2.318433995364917</v>
       </c>
       <c r="C7" t="n">
-        <v>8.046984635068569</v>
+        <v>7.056874688622927</v>
       </c>
       <c r="D7" t="n">
-        <v>7.330250110069332</v>
+        <v>7.562539066445261</v>
       </c>
       <c r="E7" t="n">
-        <v>17.31606310546199</v>
+        <v>16.9378477504331</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.169102965085156</v>
+        <v>1.480475022320814</v>
       </c>
       <c r="C8" t="n">
-        <v>5.815944284696511</v>
+        <v>4.760066404663674</v>
       </c>
       <c r="D8" t="n">
-        <v>5.50428907573807</v>
+        <v>5.832167570716808</v>
       </c>
       <c r="E8" t="n">
-        <v>12.48933632551974</v>
+        <v>12.0727089977013</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.461307662048091</v>
+        <v>1.859701552248067</v>
       </c>
       <c r="C9" t="n">
-        <v>7.372448894738579</v>
+        <v>5.841496405510203</v>
       </c>
       <c r="D9" t="n">
-        <v>6.014789544846431</v>
+        <v>6.365522661485889</v>
       </c>
       <c r="E9" t="n">
-        <v>14.8485461016331</v>
+        <v>14.06672061924416</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.748033763327794</v>
+        <v>2.264237187982898</v>
       </c>
       <c r="C10" t="n">
-        <v>9.182633735033027</v>
+        <v>7.11186081161255</v>
       </c>
       <c r="D10" t="n">
-        <v>6.560214628044259</v>
+        <v>6.933134745069453</v>
       </c>
       <c r="E10" t="n">
-        <v>17.49088212640508</v>
+        <v>16.3092327446649</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.035937439392223</v>
+        <v>2.681230517678249</v>
       </c>
       <c r="C11" t="n">
-        <v>11.15343295361698</v>
+        <v>8.565462902842789</v>
       </c>
       <c r="D11" t="n">
-        <v>7.177566151027703</v>
+        <v>7.468773386703146</v>
       </c>
       <c r="E11" t="n">
-        <v>20.3669365440369</v>
+        <v>18.71546680722419</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.31310632847629</v>
+        <v>3.111622626839585</v>
       </c>
       <c r="C12" t="n">
-        <v>13.13529563803789</v>
+        <v>10.11688879902364</v>
       </c>
       <c r="D12" t="n">
-        <v>7.731084840138862</v>
+        <v>7.999661680394705</v>
       </c>
       <c r="E12" t="n">
-        <v>23.17948680665304</v>
+        <v>21.22817310625793</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.553405596654724</v>
+        <v>3.542546850282454</v>
       </c>
       <c r="C13" t="n">
-        <v>15.0776492148718</v>
+        <v>11.73940481485001</v>
       </c>
       <c r="D13" t="n">
-        <v>8.13463088472912</v>
+        <v>8.438513542369344</v>
       </c>
       <c r="E13" t="n">
-        <v>25.76568569625564</v>
+        <v>23.72046520750181</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.465376258312874</v>
+        <v>2.058852563007113</v>
       </c>
       <c r="C14" t="n">
-        <v>10.3565252544389</v>
+        <v>8.228734367639575</v>
       </c>
       <c r="D14" t="n">
-        <v>6.217800910076749</v>
+        <v>6.386416078281139</v>
       </c>
       <c r="E14" t="n">
-        <v>18.03970242282852</v>
+        <v>16.67400300892783</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.474928663475195</v>
+        <v>2.143331952957552</v>
       </c>
       <c r="C15" t="n">
-        <v>11.29438883630588</v>
+        <v>9.040217567538862</v>
       </c>
       <c r="D15" t="n">
-        <v>6.239831328560047</v>
+        <v>6.396537897111923</v>
       </c>
       <c r="E15" t="n">
-        <v>19.00914882834112</v>
+        <v>17.58008741760834</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.684031107002724</v>
+        <v>2.509101695128785</v>
       </c>
       <c r="C16" t="n">
-        <v>13.3073545116165</v>
+        <v>10.78704125770521</v>
       </c>
       <c r="D16" t="n">
-        <v>6.6905615170568</v>
+        <v>6.884250521627654</v>
       </c>
       <c r="E16" t="n">
-        <v>21.68194713567602</v>
+        <v>20.18039347446165</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.334813631125091</v>
+        <v>2.023303478636337</v>
       </c>
       <c r="C17" t="n">
-        <v>12.18131934727653</v>
+        <v>10.07535271194261</v>
       </c>
       <c r="D17" t="n">
-        <v>6.194130972927359</v>
+        <v>6.386445530712266</v>
       </c>
       <c r="E17" t="n">
-        <v>19.71026395132898</v>
+        <v>18.48510172129122</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.492609939628681</v>
+        <v>2.316983486884728</v>
       </c>
       <c r="C18" t="n">
-        <v>14.11818975803098</v>
+        <v>11.79016160947348</v>
       </c>
       <c r="D18" t="n">
-        <v>6.574597478231167</v>
+        <v>6.795500529163741</v>
       </c>
       <c r="E18" t="n">
-        <v>22.18539717589083</v>
+        <v>20.90264562552195</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.472621556370216</v>
+        <v>2.331258098504476</v>
       </c>
       <c r="C19" t="n">
-        <v>14.99974029158236</v>
+        <v>12.63875487259329</v>
       </c>
       <c r="D19" t="n">
-        <v>6.645420757615532</v>
+        <v>6.865626767678092</v>
       </c>
       <c r="E19" t="n">
-        <v>23.11778260556811</v>
+        <v>21.83563973877586</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.612874033398915</v>
+        <v>2.603536006800287</v>
       </c>
       <c r="C20" t="n">
-        <v>17.0161322663808</v>
+        <v>14.49681057765081</v>
       </c>
       <c r="D20" t="n">
-        <v>7.015146943034881</v>
+        <v>7.333674985677759</v>
       </c>
       <c r="E20" t="n">
-        <v>25.64415324281459</v>
+        <v>24.43402157012885</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9446278235492386</v>
+        <v>1.549698568630633</v>
       </c>
       <c r="C21" t="n">
-        <v>12.26800766956153</v>
+        <v>10.58596951039842</v>
       </c>
       <c r="D21" t="n">
-        <v>5.859296100916941</v>
+        <v>6.115355537138595</v>
       </c>
       <c r="E21" t="n">
-        <v>19.07193159402771</v>
+        <v>18.25102361616765</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_51_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_51_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.296983392361542</v>
+        <v>2.588063184864887</v>
       </c>
       <c r="C3" t="n">
-        <v>4.588587540696215</v>
+        <v>7.654890186386778</v>
       </c>
       <c r="D3" t="n">
-        <v>6.070278685232742</v>
+        <v>8.14815032113242</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9558496182905</v>
+        <v>18.39110369238409</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.486449823029952</v>
+        <v>1.066170178497784</v>
       </c>
       <c r="C4" t="n">
-        <v>5.02549643309534</v>
+        <v>4.388247043429074</v>
       </c>
       <c r="D4" t="n">
-        <v>6.305201906900639</v>
+        <v>5.690554092620322</v>
       </c>
       <c r="E4" t="n">
-        <v>12.81714816302593</v>
+        <v>11.14497131454718</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.740957271283943</v>
+        <v>1.154517468763228</v>
       </c>
       <c r="C5" t="n">
-        <v>5.589195531704904</v>
+        <v>4.954460187082199</v>
       </c>
       <c r="D5" t="n">
-        <v>6.705478814784059</v>
+        <v>6.010453697124408</v>
       </c>
       <c r="E5" t="n">
-        <v>14.03563161777291</v>
+        <v>12.11943135296984</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.015756300555287</v>
+        <v>1.24919361022282</v>
       </c>
       <c r="C6" t="n">
-        <v>6.258652704346712</v>
+        <v>5.743187268617278</v>
       </c>
       <c r="D6" t="n">
-        <v>7.088295739512284</v>
+        <v>6.330534698352925</v>
       </c>
       <c r="E6" t="n">
-        <v>15.36270474441428</v>
+        <v>13.32291557719302</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.318433995364917</v>
+        <v>1.350592891736494</v>
       </c>
       <c r="C7" t="n">
-        <v>7.056874688622927</v>
+        <v>6.775888038774769</v>
       </c>
       <c r="D7" t="n">
-        <v>7.562539066445261</v>
+        <v>6.680503278868953</v>
       </c>
       <c r="E7" t="n">
-        <v>16.9378477504331</v>
+        <v>14.80698420938022</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.480475022320814</v>
+        <v>1.448234007392813</v>
       </c>
       <c r="C8" t="n">
-        <v>4.760066404663674</v>
+        <v>7.987532367234203</v>
       </c>
       <c r="D8" t="n">
-        <v>5.832167570716808</v>
+        <v>7.048889377628866</v>
       </c>
       <c r="E8" t="n">
-        <v>12.0727089977013</v>
+        <v>16.48465575225588</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.859701552248067</v>
+        <v>1.5506999428253</v>
       </c>
       <c r="C9" t="n">
-        <v>5.841496405510203</v>
+        <v>9.33639583150552</v>
       </c>
       <c r="D9" t="n">
-        <v>6.365522661485889</v>
+        <v>7.569103692724835</v>
       </c>
       <c r="E9" t="n">
-        <v>14.06672061924416</v>
+        <v>18.45619946705565</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.264237187982898</v>
+        <v>0.9858514096505619</v>
       </c>
       <c r="C10" t="n">
-        <v>7.11186081161255</v>
+        <v>6.898210973982043</v>
       </c>
       <c r="D10" t="n">
-        <v>6.933134745069453</v>
+        <v>5.980473220052124</v>
       </c>
       <c r="E10" t="n">
-        <v>16.3092327446649</v>
+        <v>13.86453560368473</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.681230517678249</v>
+        <v>0.9026875616238149</v>
       </c>
       <c r="C11" t="n">
-        <v>8.565462902842789</v>
+        <v>7.422817677223369</v>
       </c>
       <c r="D11" t="n">
-        <v>7.468773386703146</v>
+        <v>5.87269695707991</v>
       </c>
       <c r="E11" t="n">
-        <v>18.71546680722419</v>
+        <v>14.19820219592709</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.111622626839585</v>
+        <v>0.9564087960002003</v>
       </c>
       <c r="C12" t="n">
-        <v>10.11688879902364</v>
+        <v>8.808917808418313</v>
       </c>
       <c r="D12" t="n">
-        <v>7.999661680394705</v>
+        <v>6.259741172002173</v>
       </c>
       <c r="E12" t="n">
-        <v>21.22817310625793</v>
+        <v>16.02506777642069</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.542546850282454</v>
+        <v>0.7470020106843557</v>
       </c>
       <c r="C13" t="n">
-        <v>11.73940481485001</v>
+        <v>8.419114882447118</v>
       </c>
       <c r="D13" t="n">
-        <v>8.438513542369344</v>
+        <v>5.743390966953562</v>
       </c>
       <c r="E13" t="n">
-        <v>23.72046520750181</v>
+        <v>14.90950786008504</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.058852563007113</v>
+        <v>0.7978761767184253</v>
       </c>
       <c r="C14" t="n">
-        <v>8.228734367639575</v>
+        <v>9.8410095349389</v>
       </c>
       <c r="D14" t="n">
-        <v>6.386416078281139</v>
+        <v>6.140478460890269</v>
       </c>
       <c r="E14" t="n">
-        <v>16.67400300892783</v>
+        <v>16.7793641725476</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.143331952957552</v>
+        <v>0.7666762346774617</v>
       </c>
       <c r="C15" t="n">
-        <v>9.040217567538862</v>
+        <v>10.60927620089724</v>
       </c>
       <c r="D15" t="n">
-        <v>6.396537897111923</v>
+        <v>6.22492839840958</v>
       </c>
       <c r="E15" t="n">
-        <v>17.58008741760834</v>
+        <v>17.60088083398428</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.509101695128785</v>
+        <v>0.8387168812150927</v>
       </c>
       <c r="C16" t="n">
-        <v>10.78704125770521</v>
+        <v>12.33367677349859</v>
       </c>
       <c r="D16" t="n">
-        <v>6.884250521627654</v>
+        <v>6.639392826711457</v>
       </c>
       <c r="E16" t="n">
-        <v>20.18039347446165</v>
+        <v>19.81178648142514</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.023303478636337</v>
+        <v>0.511461101481461</v>
       </c>
       <c r="C17" t="n">
-        <v>10.07535271194261</v>
+        <v>9.154139571139662</v>
       </c>
       <c r="D17" t="n">
-        <v>6.386445530712266</v>
+        <v>5.5427413711596</v>
       </c>
       <c r="E17" t="n">
-        <v>18.48510172129122</v>
+        <v>15.20834204378072</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.316983486884728</v>
+        <v>0.3971856687071321</v>
       </c>
       <c r="C18" t="n">
-        <v>11.79016160947348</v>
+        <v>8.050350809777932</v>
       </c>
       <c r="D18" t="n">
-        <v>6.795500529163741</v>
+        <v>5.079758971313846</v>
       </c>
       <c r="E18" t="n">
-        <v>20.90264562552195</v>
+        <v>13.52729544979891</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.331258098504476</v>
+        <v>0.4670272003872503</v>
       </c>
       <c r="C19" t="n">
-        <v>12.63875487259329</v>
+        <v>9.910939423912399</v>
       </c>
       <c r="D19" t="n">
-        <v>6.865626767678092</v>
+        <v>5.61199385421717</v>
       </c>
       <c r="E19" t="n">
-        <v>21.83563973877586</v>
+        <v>15.98996047851682</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.603536006800287</v>
+        <v>0.529250369882413</v>
       </c>
       <c r="C20" t="n">
-        <v>14.49681057765081</v>
+        <v>11.92774373274662</v>
       </c>
       <c r="D20" t="n">
-        <v>7.333674985677759</v>
+        <v>6.121599452537604</v>
       </c>
       <c r="E20" t="n">
-        <v>24.43402157012885</v>
+        <v>18.57859355516664</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.549698568630633</v>
+        <v>0.5850921792999717</v>
       </c>
       <c r="C21" t="n">
-        <v>10.58596951039842</v>
+        <v>14.10361080462291</v>
       </c>
       <c r="D21" t="n">
-        <v>6.115355537138595</v>
+        <v>6.582971786148392</v>
       </c>
       <c r="E21" t="n">
-        <v>18.25102361616765</v>
+        <v>21.27167477007128</v>
       </c>
     </row>
   </sheetData>
